--- a/EPFU_2025/EPFU 2025 BUTT Assignments.xlsx
+++ b/EPFU_2025/EPFU 2025 BUTT Assignments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Uganda\TemperatureLoggers\EPFU_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Ashlyn_thesis\EPFU_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066EF808-8CE3-43CD-95B5-CC4DF7A3C99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E87AB3-DEDF-4EFD-8816-6F7566A0120E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database Info" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Metadata" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Loggers!$A$1:$AG$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Loggers!$A$1:$AI$1000</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Metadata!$A$1:$AC$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="342">
   <si>
     <t>Column 'Date Removed' is either termination date, date the bat died, or date the next logger was applied. Here just for general trimming in R</t>
   </si>
@@ -1065,6 +1065,9 @@
   <si>
     <t>Calibration</t>
   </si>
+  <si>
+    <t>Capture_Site</t>
+  </si>
 </sst>
 </file>
 
@@ -1223,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1256,8 +1259,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,11 +1281,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Ashlyn Sak" refreshedDate="46134.781436574071" refreshedVersion="8" recordCount="59" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Ashlyn Sak" refreshedDate="46209.467386226854" refreshedVersion="8" recordCount="59" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AG1000" sheet="Loggers"/>
+    <worksheetSource ref="A1:AI1000" sheet="Loggers"/>
   </cacheSource>
-  <cacheFields count="32">
+  <cacheFields count="35">
     <cacheField name="Serial Number" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="200000081173241" maxValue="200000081173241"/>
     </cacheField>
@@ -1300,11 +1301,11 @@
     <cacheField name="Treatment" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
         <s v="NoCo"/>
+        <s v="Primary"/>
         <s v="Dual"/>
         <s v="SHAM"/>
         <s v="Secondary"/>
         <s v="NA"/>
-        <s v="Primary"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1319,8 +1320,8 @@
         <d v="2025-09-06T00:00:00"/>
         <d v="2025-09-02T00:00:00"/>
         <d v="2025-09-09T00:00:00"/>
+        <s v="NA"/>
         <d v="2025-10-02T00:00:00"/>
-        <s v="NA"/>
         <d v="2025-09-29T00:00:00"/>
         <m/>
       </sharedItems>
@@ -1338,6 +1339,9 @@
         <m/>
       </sharedItems>
     </cacheField>
+    <cacheField name="Calibration" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
+    </cacheField>
     <cacheField name="Experiment D Died" numFmtId="0">
       <sharedItems containsBlank="1" count="11">
         <s v="D3"/>
@@ -1353,11 +1357,17 @@
         <m/>
       </sharedItems>
     </cacheField>
+    <cacheField name="Field13" caption="Field13" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
     <cacheField name="Logger location" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Notes" numFmtId="0">
       <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Field16" caption="Field16" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name=" " numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -1438,7 +1448,47 @@
     <x v="0"/>
     <d v="2025-09-10T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="CB0000008183CC41"/>
+    <s v="A2"/>
+    <s v="DMR03152"/>
+    <s v="APS36021"/>
+    <x v="1"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1466,47 +1516,16 @@
     <s v="A3"/>
     <s v="DMR03191"/>
     <s v="APS36108"/>
-    <x v="1"/>
+    <x v="2"/>
     <s v="GP 2"/>
     <s v="Male"/>
     <x v="1"/>
     <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="46000000811E9741"/>
-    <s v="A8"/>
-    <s v="DMR03182"/>
-    <s v="APS60132"/>
-    <x v="1"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1534,13 +1553,16 @@
     <s v="A4"/>
     <s v="DMR03154"/>
     <s v="APS60123"/>
-    <x v="2"/>
+    <x v="3"/>
     <s v="GP 1"/>
     <s v="Male"/>
     <x v="0"/>
     <d v="2025-09-29T00:00:00"/>
     <x v="1"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1568,13 +1590,16 @@
     <s v="A5"/>
     <s v="DMR03162"/>
     <s v="APS36106"/>
-    <x v="1"/>
+    <x v="2"/>
     <s v="GP 1"/>
     <s v="Female"/>
     <x v="1"/>
     <d v="2025-09-29T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1602,13 +1627,16 @@
     <s v="A6"/>
     <s v="DMR03161"/>
     <s v="APS60125"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="GP 2"/>
     <s v="Female"/>
     <x v="1"/>
     <d v="2025-10-08T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1642,7 +1670,10 @@
     <x v="2"/>
     <d v="2025-09-16T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1666,17 +1697,20 @@
     <m/>
   </r>
   <r>
-    <s v="CD00000081881A41"/>
-    <s v="B9"/>
-    <s v="DMR03158"/>
-    <s v="APS36010_boost"/>
+    <s v="46000000811E9741"/>
+    <s v="A8"/>
+    <s v="DMR03182"/>
+    <s v="APS60132"/>
+    <x v="2"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
     <x v="1"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
+    <d v="2025-10-14T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1710,7 +1744,10 @@
     <x v="0"/>
     <d v="2025-09-15T00:00:00"/>
     <x v="2"/>
+    <n v="1"/>
     <x v="4"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1734,18 +1771,21 @@
     <m/>
   </r>
   <r>
-    <s v="9A000000811E9341"/>
-    <s v="S2"/>
-    <s v="DMR03187"/>
-    <s v="APS36036"/>
+    <s v="DF00000081814041"/>
+    <s v="B1"/>
+    <s v="DMR03181"/>
+    <s v="APS60135"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Butt"/>
+    <s v="Old Danville Highway Barn"/>
+    <s v="Off-centered"/>
+    <s v="Off-centered to avoid wound of pittag "/>
     <m/>
     <m/>
     <m/>
@@ -1772,13 +1812,16 @@
     <s v="B2"/>
     <s v="NA"/>
     <s v="NA"/>
-    <x v="4"/>
+    <x v="5"/>
     <s v=""/>
     <s v=""/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="NA"/>
     <x v="3"/>
+    <n v="1"/>
     <x v="5"/>
+    <s v=""/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1802,53 +1845,59 @@
     <m/>
   </r>
   <r>
-    <s v="C5000000811EA541"/>
-    <s v="S5"/>
-    <s v="DMR03162"/>
-    <s v="APS36106_boost"/>
+    <s v="0700000081190F41"/>
+    <s v="B3"/>
+    <s v="DMR03155"/>
+    <s v="APS36033"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="D8000000818C4541"/>
+    <s v="B4"/>
+    <s v="DMR03185"/>
+    <s v="APS36103"/>
+    <x v="4"/>
     <s v="GP 1"/>
     <s v="Female"/>
-    <x v="5"/>
+    <x v="1"/>
     <d v="2025-10-14T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="7D0000008122D241"/>
-    <s v="S7"/>
-    <s v="DMR03159"/>
-    <s v="APS36007_boost"/>
-    <x v="1"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <s v="Data messed up probably have to throw out"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1874,13 +1923,16 @@
     <s v="B5"/>
     <s v="DMR03175"/>
     <s v="APS36101"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="GP 1"/>
     <s v="Male"/>
     <x v="1"/>
     <d v="2025-09-11T00:00:00"/>
     <x v="2"/>
+    <n v="1"/>
     <x v="0"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1908,13 +1960,16 @@
     <s v="B6"/>
     <s v="DMR03160"/>
     <s v="APS60109"/>
-    <x v="2"/>
+    <x v="3"/>
     <s v="GP 1"/>
     <s v="Female"/>
     <x v="0"/>
     <d v="2025-09-09T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="6"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1948,7 +2003,158 @@
     <x v="0"/>
     <d v="2025-09-29T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="63000000811C2F41"/>
+    <s v="B8"/>
+    <s v="DMR03180"/>
+    <s v="APS60146"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="2"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="CD00000081881A41"/>
+    <s v="B9"/>
+    <s v="DMR03158"/>
+    <s v="APS36010_boost"/>
+    <x v="2"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="AC00000081223941"/>
+    <s v="C1"/>
+    <s v="DMR03184"/>
+    <s v="APS60160"/>
+    <x v="1"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="BB000000818AFE41"/>
+    <s v="C2"/>
+    <s v="DMR03153"/>
+    <s v="APS60079"/>
+    <x v="0"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="2"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1982,9 +2188,197 @@
     <x v="2"/>
     <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
     <s v="Butt"/>
     <s v="Some bad data points"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="9B000000811F0F41"/>
+    <s v="C4"/>
+    <s v="DMR03186"/>
+    <s v="APS36057_boost"/>
+    <x v="1"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="1D00000081175641"/>
+    <s v="C5"/>
+    <s v="DMR03157"/>
+    <s v="APS60118"/>
+    <x v="1"/>
+    <s v="GP 1"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="3C000000811C1941"/>
+    <s v="C6"/>
+    <s v="DMR03164"/>
+    <s v="APS60088"/>
+    <x v="1"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="19000000811D8A41"/>
+    <s v="C7"/>
+    <s v="DMR03151"/>
+    <s v="APS36011"/>
+    <x v="2"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="7"/>
+    <s v="Scott's House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="BD000000811A6E41"/>
+    <s v="C8"/>
+    <s v="DMR03173"/>
+    <s v="APS60086"/>
+    <x v="1"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-09-13T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="3"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2016,7 +2410,750 @@
     <x v="0"/>
     <d v="2025-10-14T00:00:00"/>
     <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="60000000811CB941"/>
+    <s v="J1"/>
+    <s v="DMR03177"/>
+    <s v="APS36050"/>
+    <x v="4"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="8C00000081197141"/>
+    <s v="J2"/>
+    <s v="DMR03172"/>
+    <s v="APS60074"/>
+    <x v="4"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="06000000818A0441"/>
+    <s v="J3"/>
+    <s v="DMR03188"/>
+    <s v="APS36081"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="2"/>
+    <d v="2025-10-04T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="8"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="E6000000811F0341"/>
+    <s v="J4"/>
+    <s v="DMR03166"/>
+    <s v="APS60100"/>
+    <x v="3"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="0"/>
+    <d v="2025-09-09T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="6"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="1200000081836B41"/>
+    <s v="J5"/>
+    <s v="DMR03168"/>
+    <s v="APS60115"/>
+    <x v="4"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-09-29T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="1C000000811B7F41"/>
+    <s v="J6"/>
+    <s v="DMR03192"/>
+    <s v="APS60113_boost"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="B00000008121E041"/>
+    <s v="J7"/>
+    <s v="DMR03192"/>
+    <s v="APS60113"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="2"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <s v="Butt"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="7E00000081224441"/>
+    <s v="J8"/>
+    <s v="DMR03156"/>
+    <s v="APS60111"/>
+    <x v="3"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="8D000000818A7A41"/>
+    <s v="J9"/>
+    <s v="DMR03163"/>
+    <s v="APS60156"/>
+    <x v="4"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="2B0000008189E941"/>
+    <s v="K1"/>
+    <s v="DMR03171"/>
+    <s v="APS60134"/>
+    <x v="2"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-09-12T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="9"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="01000000811F6C41"/>
+    <s v="K2"/>
+    <s v="DMR03176"/>
+    <s v="APS60082"/>
+    <x v="1"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Troxelville House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="7D0000008122D241"/>
+    <s v="K3"/>
+    <s v="DMR03189"/>
+    <s v="APS60112"/>
+    <x v="4"/>
+    <s v="GP 1"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-09-13T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="3"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="CB0000008181FE41"/>
+    <s v="K4"/>
+    <s v="DMR03178"/>
+    <s v="APS60141"/>
+    <x v="0"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="B40000008187B741"/>
+    <s v="K5"/>
+    <s v="DMR03183"/>
+    <s v="APS36026"/>
+    <x v="1"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <s v="Some bad data"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="D3000000811C3A41"/>
+    <s v="K6"/>
+    <s v="DMR03179"/>
+    <s v="APS60065"/>
+    <x v="3"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="0"/>
+    <d v="2025-09-13T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="3"/>
+    <s v="Scott's House"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="4D00000081190241"/>
+    <s v="K7"/>
+    <s v="DMR03158"/>
+    <s v="APS36010"/>
+    <x v="2"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="3D000000818A6F41"/>
+    <s v="K8"/>
+    <s v="DMR03159"/>
+    <s v="APS36007"/>
+    <x v="2"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="770000008187D741"/>
+    <s v="K9"/>
+    <s v="DMR03186"/>
+    <s v="APS36057"/>
+    <x v="1"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="B5000000818B9E41"/>
+    <s v="S1"/>
+    <s v="DMR03194"/>
+    <s v="APS36027"/>
+    <x v="4"/>
+    <s v="GP 2"/>
+    <s v="Male"/>
+    <x v="2"/>
+    <d v="2025-09-15T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="9"/>
+    <s v="Old Danville Highway Barn"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="9A000000811E9341"/>
+    <s v="S2"/>
+    <s v="DMR03187"/>
+    <s v="APS36036"/>
+    <x v="2"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
+    <s v="Butt"/>
     <m/>
     <m/>
     <m/>
@@ -2050,9 +3187,12 @@
     <x v="5"/>
     <d v="2025-10-14T00:00:00"/>
     <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
+    <s v="Old Danville Highway Barn"/>
     <m/>
     <s v="Same serial umber as K6"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2074,17 +3214,57 @@
     <m/>
   </r>
   <r>
-    <s v="BB000000818AFE41"/>
-    <s v="C2"/>
-    <s v="DMR03153"/>
-    <s v="APS60079"/>
+    <s v="2B0000008189E941"/>
+    <s v="S4"/>
+    <s v="DMR03163"/>
+    <s v="APS60156_boost"/>
+    <x v="4"/>
+    <s v="GP 2"/>
+    <s v="Female"/>
+    <x v="4"/>
+    <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="C5000000811EA541"/>
+    <s v="S5"/>
+    <s v="DMR03162"/>
+    <s v="APS36106_boost"/>
     <x v="2"/>
-    <d v="2025-10-02T00:00:00"/>
+    <s v="GP 1"/>
+    <s v="Female"/>
+    <x v="5"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
-    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2115,10 +3295,13 @@
     <x v="0"/>
     <s v="GP 2"/>
     <s v="Male"/>
-    <x v="3"/>
+    <x v="4"/>
     <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
+    <s v="Scott's House"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2142,18 +3325,21 @@
     <m/>
   </r>
   <r>
-    <s v="CB0000008183CC41"/>
-    <s v="A2"/>
-    <s v="DMR03152"/>
-    <s v="APS36021"/>
-    <x v="5"/>
+    <s v="7D0000008122D241"/>
+    <s v="S7"/>
+    <s v="DMR03159"/>
+    <s v="APS36007_boost"/>
+    <x v="2"/>
     <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="1"/>
+    <s v="Female"/>
+    <x v="4"/>
     <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
-    <m/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
+    <s v="Data messed up probably have to throw out"/>
     <m/>
     <m/>
     <m/>
@@ -2176,85 +3362,20 @@
     <m/>
   </r>
   <r>
-    <s v="AC00000081223941"/>
-    <s v="C1"/>
-    <s v="DMR03184"/>
-    <s v="APS60160"/>
+    <s v="1C00000081866F41"/>
+    <s v="S8"/>
+    <s v="DMR03154"/>
+    <s v="APS60123_boost"/>
+    <x v="3"/>
+    <s v="GP 1"/>
+    <s v="Male"/>
     <x v="5"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
     <d v="2025-10-14T00:00:00"/>
     <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="3C000000811C1941"/>
-    <s v="C6"/>
-    <s v="DMR03164"/>
-    <s v="APS60088"/>
-    <x v="5"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="2"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="19000000811D8A41"/>
-    <s v="C7"/>
-    <s v="DMR03151"/>
-    <s v="APS36011"/>
-    <x v="1"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="0"/>
-    <x v="7"/>
+    <s v="Scott's House"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2279,16 +3400,19 @@
   </r>
   <r>
     <s v="BD000000811A6E41"/>
-    <s v="C8"/>
-    <s v="DMR03173"/>
-    <s v="APS60086"/>
-    <x v="5"/>
+    <s v="S9"/>
+    <s v="DMR03168"/>
+    <s v="APS60115_boost"/>
+    <x v="4"/>
     <s v="GP 1"/>
     <s v="Female"/>
+    <x v="5"/>
+    <d v="2025-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
-    <d v="2025-09-13T00:00:00"/>
-    <x v="0"/>
-    <x v="3"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2312,256 +3436,21 @@
     <m/>
   </r>
   <r>
-    <s v="9B000000811F0F41"/>
-    <s v="C4"/>
-    <s v="DMR03186"/>
-    <s v="APS36057_boost"/>
+    <s v="B5000000818B9E41"/>
+    <s v="V1"/>
+    <s v="NA"/>
+    <s v="NA"/>
     <x v="5"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
+    <s v=""/>
+    <s v=""/>
     <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="60000000811CB941"/>
-    <s v="J1"/>
-    <s v="DMR03177"/>
-    <s v="APS36050"/>
-    <x v="3"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="2"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="1D00000081175641"/>
-    <s v="C5"/>
-    <s v="DMR03157"/>
-    <s v="APS60118"/>
+    <s v="NA"/>
+    <x v="4"/>
+    <n v="2"/>
     <x v="5"/>
-    <s v="GP 1"/>
-    <s v="Male"/>
-    <x v="1"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="06000000818A0441"/>
-    <s v="J3"/>
-    <s v="DMR03188"/>
-    <s v="APS36081"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="2"/>
-    <d v="2025-10-04T00:00:00"/>
-    <x v="0"/>
-    <x v="8"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="E6000000811F0341"/>
-    <s v="J4"/>
-    <s v="DMR03166"/>
-    <s v="APS60100"/>
-    <x v="2"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="0"/>
-    <d v="2025-09-09T00:00:00"/>
-    <x v="0"/>
-    <x v="6"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="1200000081836B41"/>
-    <s v="J5"/>
-    <s v="DMR03168"/>
-    <s v="APS60115"/>
-    <x v="3"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-09-29T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="B40000008187B741"/>
-    <s v="K5"/>
-    <s v="DMR03183"/>
-    <s v="APS36026"/>
-    <x v="5"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <s v="Some bad data"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="B00000008121E041"/>
-    <s v="J7"/>
-    <s v="DMR03192"/>
-    <s v="APS60113"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="2"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Butt"/>
+    <s v=""/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2588,727 +3477,16 @@
     <s v="V2"/>
     <s v="DMR03164"/>
     <s v="APS60088_boost"/>
-    <x v="5"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="8D000000818A7A41"/>
-    <s v="J9"/>
-    <s v="DMR03163"/>
-    <s v="APS60156"/>
-    <x v="3"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="1"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="2B0000008189E941"/>
-    <s v="K1"/>
-    <s v="DMR03171"/>
-    <s v="APS60134"/>
-    <x v="1"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-09-12T00:00:00"/>
-    <x v="0"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="01000000811F6C41"/>
-    <s v="K2"/>
-    <s v="DMR03176"/>
-    <s v="APS60082"/>
-    <x v="5"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="2"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="7D0000008122D241"/>
-    <s v="K3"/>
-    <s v="DMR03189"/>
-    <s v="APS60112"/>
-    <x v="3"/>
-    <s v="GP 1"/>
-    <s v="Male"/>
-    <x v="1"/>
-    <d v="2025-09-13T00:00:00"/>
-    <x v="0"/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="CB0000008181FE41"/>
-    <s v="K4"/>
-    <s v="DMR03178"/>
-    <s v="APS60141"/>
-    <x v="0"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="2"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="2"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="D8000000818C4541"/>
-    <s v="B4"/>
-    <s v="DMR03185"/>
-    <s v="APS36103"/>
-    <x v="3"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="D3000000811C3A41"/>
-    <s v="K6"/>
-    <s v="DMR03179"/>
-    <s v="APS60065"/>
-    <x v="2"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="0"/>
-    <d v="2025-09-13T00:00:00"/>
-    <x v="0"/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="4D00000081190241"/>
-    <s v="K7"/>
-    <s v="DMR03158"/>
-    <s v="APS36010"/>
-    <x v="1"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="2"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="3D000000818A6F41"/>
-    <s v="K8"/>
-    <s v="DMR03159"/>
-    <s v="APS36007"/>
     <x v="1"/>
     <s v="GP 2"/>
     <s v="Female"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="770000008187D741"/>
-    <s v="K9"/>
-    <s v="DMR03186"/>
-    <s v="APS36057"/>
-    <x v="5"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="1"/>
-    <d v="2025-10-02T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="B5000000818B9E41"/>
-    <s v="S1"/>
-    <s v="DMR03194"/>
-    <s v="APS36027"/>
-    <x v="3"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="2"/>
-    <d v="2025-09-15T00:00:00"/>
-    <x v="0"/>
-    <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="8C00000081197141"/>
-    <s v="J2"/>
-    <s v="DMR03172"/>
-    <s v="APS60074"/>
-    <x v="3"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="1"/>
+    <x v="4"/>
     <d v="2025-10-17T00:00:00"/>
     <x v="0"/>
+    <n v="2"/>
     <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="2B0000008189E941"/>
-    <s v="S4"/>
-    <s v="DMR03163"/>
-    <s v="APS60156_boost"/>
-    <x v="3"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="BD000000811A6E41"/>
-    <s v="S9"/>
-    <s v="DMR03168"/>
-    <s v="APS60115_boost"/>
-    <x v="3"/>
-    <s v="GP 1"/>
-    <s v="Female"/>
-    <x v="5"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="DF00000081814041"/>
-    <s v="B1"/>
-    <s v="DMR03181"/>
-    <s v="APS60135"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="2"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Off-centered"/>
-    <s v="Off-centered to avoid wound of pittag "/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="0700000081190F41"/>
-    <s v="B3"/>
-    <s v="DMR03155"/>
-    <s v="APS36033"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="2"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="63000000811C2F41"/>
-    <s v="B8"/>
-    <s v="DMR03180"/>
-    <s v="APS60146"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="2"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="1C000000811B7F41"/>
-    <s v="J6"/>
-    <s v="DMR03192"/>
-    <s v="APS60113_boost"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Male"/>
-    <x v="3"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="7E00000081224441"/>
-    <s v="J8"/>
-    <s v="DMR03156"/>
-    <s v="APS60111"/>
-    <x v="2"/>
-    <s v="GP 2"/>
-    <s v="Female"/>
-    <x v="2"/>
-    <d v="2025-10-17T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="B5000000818B9E41"/>
-    <s v="V1"/>
-    <s v="NA"/>
-    <s v="NA"/>
-    <x v="4"/>
-    <s v=""/>
-    <s v=""/>
-    <x v="4"/>
-    <s v="NA"/>
-    <x v="4"/>
-    <x v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <s v="1C00000081866F41"/>
-    <s v="S8"/>
-    <s v="DMR03154"/>
-    <s v="APS60123_boost"/>
-    <x v="2"/>
-    <s v="GP 1"/>
-    <s v="Male"/>
-    <x v="5"/>
-    <d v="2025-10-14T00:00:00"/>
-    <x v="0"/>
-    <x v="1"/>
+    <s v="Warriors Mark Farmhouse"/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -3336,13 +3514,16 @@
     <s v="V3"/>
     <s v="NA"/>
     <s v="NA"/>
-    <x v="4"/>
+    <x v="5"/>
     <s v=""/>
     <s v=""/>
+    <x v="3"/>
+    <m/>
     <x v="4"/>
-    <m/>
-    <x v="4"/>
+    <n v="2"/>
     <x v="5"/>
+    <s v=""/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -3376,7 +3557,10 @@
     <x v="6"/>
     <m/>
     <x v="5"/>
+    <m/>
     <x v="10"/>
+    <s v=""/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -3410,7 +3594,10 @@
     <x v="6"/>
     <m/>
     <x v="5"/>
+    <m/>
     <x v="10"/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -3439,19 +3626,19 @@
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Pivot Table 2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0">
   <location ref="A4:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
+  <pivotFields count="35">
     <pivotField name="Serial Number" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Logger Name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Bat Band" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Bat Pittag" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Treatment" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items count="8">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
         <item x="3"/>
-        <item x="2"/>
         <item x="6"/>
         <item t="default"/>
       </items>
@@ -3460,12 +3647,12 @@
     <pivotField name="Sex" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Date Attached" axis="axisCol" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items count="8">
-        <item x="4"/>
+        <item x="3"/>
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
         <item x="5"/>
-        <item x="3"/>
+        <item x="4"/>
         <item x="6"/>
         <item t="default"/>
       </items>
@@ -3482,6 +3669,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" includeNewItemsInFilter="1"/>
     <pivotField name="Experiment D Died" axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="12">
         <item x="0"/>
@@ -3498,8 +3686,10 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" includeNewItemsInFilter="1"/>
     <pivotField name="Logger location" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Notes" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" includeNewItemsInFilter="1"/>
     <pivotField name=" " compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name=" 2" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name=" 3" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -3544,7 +3734,7 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="9" hier="0"/>
-    <pageField fld="10" hier="0"/>
+    <pageField fld="11" hier="0"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="COUNTA of BUTT Status " fld="9" subtotal="count" baseField="0"/>
@@ -3777,14 +3967,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="11" max="11" width="12.6328125" style="27"/>
+    <col min="14" max="14" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3822,17 +4012,15 @@
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="P1" s="2"/>
       <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
@@ -3884,8 +4072,14 @@
       <c r="AG1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -3919,15 +4113,19 @@
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="str">
         <f t="array" ref="L2">IFERROR(INDEX(Metadata!O:O, MATCH(C2,Metadata!A:A, 0)),"")</f>
         <v>D3</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C2,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>97</v>
       </c>
@@ -3961,15 +4159,19 @@
       <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="str">
         <f t="array" ref="L3">IFERROR(INDEX(Metadata!O:O, MATCH(C3,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C3,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -4003,15 +4205,19 @@
       <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="str">
         <f t="array" ref="L4">IFERROR(INDEX(Metadata!O:O, MATCH(C4,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C4,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -4045,15 +4251,19 @@
       <c r="J5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="str">
         <f t="array" ref="L5">IFERROR(INDEX(Metadata!O:O, MATCH(C5,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C5,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>200000081173241</v>
       </c>
@@ -4087,15 +4297,19 @@
       <c r="J6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="str">
         <f t="array" ref="L6">IFERROR(INDEX(Metadata!O:O, MATCH(C6,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C6,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -4129,15 +4343,19 @@
       <c r="J7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="str">
         <f t="array" ref="L7">IFERROR(INDEX(Metadata!O:O, MATCH(C7,Metadata!A:A, 0)),"")</f>
         <v>D27</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C7,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -4171,15 +4389,19 @@
       <c r="J8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="str">
         <f t="array" ref="L8">IFERROR(INDEX(Metadata!O:O, MATCH(C8,Metadata!A:A, 0)),"")</f>
         <v>D5</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C8,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -4213,15 +4435,19 @@
       <c r="J9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="str">
         <f t="array" ref="L9">IFERROR(INDEX(Metadata!O:O, MATCH(C9,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C9,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -4255,15 +4481,19 @@
       <c r="J10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="str">
         <f t="array" ref="L10">IFERROR(INDEX(Metadata!O:O, MATCH(C10,Metadata!A:A, 0)),"")</f>
         <v>D6</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C10,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>193</v>
       </c>
@@ -4297,21 +4527,26 @@
       <c r="J11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="str">
         <f t="array" ref="L11">IFERROR(INDEX(Metadata!O:O, MATCH(C11,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C11,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -4344,14 +4579,18 @@
       <c r="J12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C12,Metadata!A:A, 0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>199</v>
       </c>
@@ -4385,15 +4624,19 @@
       <c r="J13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="str">
         <f t="array" ref="L13">IFERROR(INDEX(Metadata!O:O, MATCH(C13,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C13,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>170</v>
       </c>
@@ -4427,15 +4670,19 @@
       <c r="J14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="str">
         <f t="array" ref="L14">IFERROR(INDEX(Metadata!O:O, MATCH(C14,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C14,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -4469,15 +4716,19 @@
       <c r="J15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="str">
         <f t="array" ref="L15">IFERROR(INDEX(Metadata!O:O, MATCH(C15,Metadata!A:A, 0)),"")</f>
         <v>D3</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C15,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>72</v>
       </c>
@@ -4511,15 +4762,19 @@
       <c r="J16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="str">
         <f t="array" ref="L16">IFERROR(INDEX(Metadata!O:O, MATCH(C16,Metadata!A:A, 0)),"")</f>
         <v>D1</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C16,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>76</v>
       </c>
@@ -4553,15 +4808,19 @@
       <c r="J17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="str">
         <f t="array" ref="L17">IFERROR(INDEX(Metadata!O:O, MATCH(C17,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C17,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>203</v>
       </c>
@@ -4595,15 +4854,19 @@
       <c r="J18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="str">
         <f t="array" ref="L18">IFERROR(INDEX(Metadata!O:O, MATCH(C18,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C18,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -4637,15 +4900,19 @@
       <c r="J19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="str">
         <f t="array" ref="L19">IFERROR(INDEX(Metadata!O:O, MATCH(C19,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C19,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>101</v>
       </c>
@@ -4679,15 +4946,19 @@
       <c r="J20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="str">
         <f t="array" ref="L20">IFERROR(INDEX(Metadata!O:O, MATCH(C20,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C20,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -4721,15 +4992,19 @@
       <c r="J21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="26">
+      <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="str">
         <f t="array" ref="L21">IFERROR(INDEX(Metadata!O:O, MATCH(C21,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C21,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -4763,21 +5038,26 @@
       <c r="J22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="str">
         <f t="array" ref="L22">IFERROR(INDEX(Metadata!O:O, MATCH(C22,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C22,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>117</v>
       </c>
@@ -4811,15 +5091,19 @@
       <c r="J23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="str">
         <f t="array" ref="L23">IFERROR(INDEX(Metadata!O:O, MATCH(C23,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C23,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>125</v>
       </c>
@@ -4853,15 +5137,19 @@
       <c r="J24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="str">
         <f t="array" ref="L24">IFERROR(INDEX(Metadata!O:O, MATCH(C24,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C24,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>105</v>
       </c>
@@ -4895,15 +5183,19 @@
       <c r="J25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="str">
         <f t="array" ref="L25">IFERROR(INDEX(Metadata!O:O, MATCH(C25,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M25" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C25,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>109</v>
       </c>
@@ -4937,15 +5229,19 @@
       <c r="J26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="str">
         <f t="array" ref="L26">IFERROR(INDEX(Metadata!O:O, MATCH(C26,Metadata!A:A, 0)),"")</f>
         <v>D21</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M26" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C26,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>113</v>
       </c>
@@ -4979,15 +5275,19 @@
       <c r="J27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="str">
         <f t="array" ref="L27">IFERROR(INDEX(Metadata!O:O, MATCH(C27,Metadata!A:A, 0)),"")</f>
         <v>D5</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M27" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C27,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
@@ -5021,15 +5321,19 @@
       <c r="J28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="26">
+      <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="str">
         <f t="array" ref="L28">IFERROR(INDEX(Metadata!O:O, MATCH(C28,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M28" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C28,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -5063,15 +5367,19 @@
       <c r="J29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K29" s="26">
+      <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="str">
         <f t="array" ref="L29">IFERROR(INDEX(Metadata!O:O, MATCH(C29,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M29" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C29,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>187</v>
       </c>
@@ -5105,15 +5413,19 @@
       <c r="J30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="str">
         <f t="array" ref="L30">IFERROR(INDEX(Metadata!O:O, MATCH(C30,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M30" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C30,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>129</v>
       </c>
@@ -5147,15 +5459,19 @@
       <c r="J31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="str">
         <f t="array" ref="L31">IFERROR(INDEX(Metadata!O:O, MATCH(C31,Metadata!A:A, 0)),"")</f>
         <v>D23</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M31" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C31,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>133</v>
       </c>
@@ -5189,15 +5505,19 @@
       <c r="J32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="str">
         <f t="array" ref="L32">IFERROR(INDEX(Metadata!O:O, MATCH(C32,Metadata!A:A, 0)),"")</f>
         <v>D1</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M32" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C32,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>137</v>
       </c>
@@ -5231,15 +5551,19 @@
       <c r="J33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="str">
         <f t="array" ref="L33">IFERROR(INDEX(Metadata!O:O, MATCH(C33,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M33" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C33,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>207</v>
       </c>
@@ -5273,15 +5597,19 @@
       <c r="J34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K34" s="26">
+      <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="str">
         <f t="array" ref="L34">IFERROR(INDEX(Metadata!O:O, MATCH(C34,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M34" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C34,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>146</v>
       </c>
@@ -5315,18 +5643,22 @@
       <c r="J35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="26">
+      <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="str">
         <f t="array" ref="L35">IFERROR(INDEX(Metadata!O:O, MATCH(C35,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C35,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>209</v>
       </c>
@@ -5360,15 +5692,19 @@
       <c r="J36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K36" s="26">
+      <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="str">
         <f t="array" ref="L36">IFERROR(INDEX(Metadata!O:O, MATCH(C36,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M36" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C36,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>151</v>
       </c>
@@ -5402,15 +5738,19 @@
       <c r="J37" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K37" s="26">
+      <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="str">
         <f t="array" ref="L37">IFERROR(INDEX(Metadata!O:O, MATCH(C37,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M37" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C37,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>155</v>
       </c>
@@ -5444,15 +5784,19 @@
       <c r="J38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K38" s="26">
+      <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="str">
-        <f t="array" ref="L38">IFERROR(INDEX(Metadata!O:O, MATCH(C38,Metadata!A:A, 0)),"")</f>
+        <f>IFERROR(INDEX(Metadata!O:O, MATCH(C38,Metadata!A:A, 0)),"")</f>
         <v>D4</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M38" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C38,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>159</v>
       </c>
@@ -5486,15 +5830,19 @@
       <c r="J39" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K39" s="26">
+      <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="str">
         <f t="array" ref="L39">IFERROR(INDEX(Metadata!O:O, MATCH(C39,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M39" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C39,Metadata!A:A, 0)),"")</f>
+        <v>Troxelville House</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>63</v>
       </c>
@@ -5528,15 +5876,19 @@
       <c r="J40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="26">
+      <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="str">
         <f t="array" ref="L40">IFERROR(INDEX(Metadata!O:O, MATCH(C40,Metadata!A:A, 0)),"")</f>
         <v>D5</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M40" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C40,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>166</v>
       </c>
@@ -5570,15 +5922,19 @@
       <c r="J41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K41" s="26">
+      <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="str">
         <f t="array" ref="L41">IFERROR(INDEX(Metadata!O:O, MATCH(C41,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M41" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C41,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>141</v>
       </c>
@@ -5612,18 +5968,23 @@
       <c r="J42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K42" s="26">
+      <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="str">
         <f t="array" ref="L42">IFERROR(INDEX(Metadata!O:O, MATCH(C42,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="M42" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C42,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>89</v>
       </c>
@@ -5657,15 +6018,19 @@
       <c r="J43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="26">
+      <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="str">
         <f t="array" ref="L43">IFERROR(INDEX(Metadata!O:O, MATCH(C43,Metadata!A:A, 0)),"")</f>
         <v>D5</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M43" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C43,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>177</v>
       </c>
@@ -5699,15 +6064,19 @@
       <c r="J44" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K44" s="26">
+      <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="str">
         <f t="array" ref="L44">IFERROR(INDEX(Metadata!O:O, MATCH(C44,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M44" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C44,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>179</v>
       </c>
@@ -5741,15 +6110,19 @@
       <c r="J45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K45" s="26">
+      <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="str">
         <f t="array" ref="L45">IFERROR(INDEX(Metadata!O:O, MATCH(C45,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M45" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C45,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>181</v>
       </c>
@@ -5783,15 +6156,19 @@
       <c r="J46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K46" s="26">
+      <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="str">
         <f t="array" ref="L46">IFERROR(INDEX(Metadata!O:O, MATCH(C46,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M46" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C46,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>183</v>
       </c>
@@ -5825,15 +6202,19 @@
       <c r="J47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K47" s="26">
+      <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="str">
         <f t="array" ref="L47">IFERROR(INDEX(Metadata!O:O, MATCH(C47,Metadata!A:A, 0)),"")</f>
         <v>D4</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M47" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C47,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -5867,18 +6248,22 @@
       <c r="J48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="26">
+      <c r="K48" s="1">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="str">
         <f t="array" ref="L48">IFERROR(INDEX(Metadata!O:O, MATCH(C48,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="M48" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C48,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>89</v>
       </c>
@@ -5912,18 +6297,23 @@
       <c r="J49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K49" s="26">
+      <c r="K49" s="1">
         <v>2</v>
       </c>
       <c r="L49" s="1" t="str">
         <f t="array" ref="L49">IFERROR(INDEX(Metadata!O:O, MATCH(C49,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="M49" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C49,Metadata!A:A, 0)),"")</f>
+        <v>Old Danville Highway Barn</v>
+      </c>
+      <c r="O49" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>155</v>
       </c>
@@ -5957,15 +6347,19 @@
       <c r="J50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K50" s="26">
+      <c r="K50" s="1">
         <v>2</v>
       </c>
       <c r="L50" s="1" t="str">
         <f t="array" ref="L50">IFERROR(INDEX(Metadata!O:O, MATCH(C50,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M50" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C50,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -5999,15 +6393,19 @@
       <c r="J51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="26">
+      <c r="K51" s="1">
         <v>2</v>
       </c>
       <c r="L51" s="1" t="str">
         <f t="array" ref="L51">IFERROR(INDEX(Metadata!O:O, MATCH(C51,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M51" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C51,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>76</v>
       </c>
@@ -6041,15 +6439,19 @@
       <c r="J52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="26">
+      <c r="K52" s="1">
         <v>2</v>
       </c>
       <c r="L52" s="1" t="str">
         <f t="array" ref="L52">IFERROR(INDEX(Metadata!O:O, MATCH(C52,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M52" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C52,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -6083,18 +6485,23 @@
       <c r="J53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K53" s="26">
+      <c r="K53" s="1">
         <v>2</v>
       </c>
       <c r="L53" s="1" t="str">
         <f t="array" ref="L53">IFERROR(INDEX(Metadata!O:O, MATCH(C53,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-      <c r="N53" s="1" t="s">
+      <c r="M53" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C53,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+      <c r="O53" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="P53" s="1"/>
+    </row>
+    <row r="54" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>15</v>
       </c>
@@ -6128,15 +6535,19 @@
       <c r="J54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K54" s="26">
+      <c r="K54" s="1">
         <v>2</v>
       </c>
       <c r="L54" s="1" t="str">
         <f t="array" ref="L54">IFERROR(INDEX(Metadata!O:O, MATCH(C54,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M54" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C54,Metadata!A:A, 0)),"")</f>
+        <v>Scott's House</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>113</v>
       </c>
@@ -6170,15 +6581,19 @@
       <c r="J55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="26">
+      <c r="K55" s="1">
         <v>2</v>
       </c>
       <c r="L55" s="1" t="str">
         <f t="array" ref="L55">IFERROR(INDEX(Metadata!O:O, MATCH(C55,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M55" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C55,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>183</v>
       </c>
@@ -6211,14 +6626,18 @@
       <c r="J56" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K56" s="26">
+      <c r="K56" s="1">
         <v>2</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M56" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C56,Metadata!A:A, 0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>137</v>
       </c>
@@ -6252,15 +6671,19 @@
       <c r="J57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="26">
+      <c r="K57" s="1">
         <v>2</v>
       </c>
       <c r="L57" s="1" t="str">
         <f t="array" ref="L57">IFERROR(INDEX(Metadata!O:O, MATCH(C57,Metadata!A:A, 0)),"")</f>
         <v>D36</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M57" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C57,Metadata!A:A, 0)),"")</f>
+        <v>Warriors Mark Farmhouse</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>72</v>
       </c>
@@ -6290,21 +6713,29 @@
       <c r="J58" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K58" s="26">
+      <c r="K58" s="1">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="M58" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C58,Metadata!A:A, 0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="M59" s="1" t="str">
+        <f>IFERROR(INDEX(Metadata!D:D, MATCH(C59,Metadata!A:A, 0)),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1000" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG1000">
+  <autoFilter ref="A1:AI1000" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI1000">
       <sortCondition ref="B1:B1000"/>
     </sortState>
   </autoFilter>
